--- a/diseases/d038/2000-2004.xlsx
+++ b/diseases/d038/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>886</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>17.11679887268685</v>
       </c>
@@ -1693,9 +1690,6 @@
       <c r="O7" t="n">
         <v>431</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>8.326569203304778</v>
       </c>
@@ -2473,9 +2467,6 @@
       <c r="O11" t="n">
         <v>85</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>1.642130817357091</v>
       </c>
@@ -3253,9 +3244,6 @@
       <c r="O15" t="n">
         <v>28</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.5409372104235123</v>
       </c>
@@ -4033,9 +4021,6 @@
       <c r="O19" t="n">
         <v>7</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.1352343026058781</v>
       </c>
@@ -4813,9 +4798,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -5593,9 +5575,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6373,9 +6352,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -7153,9 +7129,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7933,9 +7906,6 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -8713,9 +8683,6 @@
       <c r="O43" t="n">
         <v>16</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.3091069773848642</v>
       </c>
@@ -9493,9 +9460,6 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>1.043236048673917</v>
       </c>
@@ -10273,9 +10237,6 @@
       <c r="O51" t="n">
         <v>423</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>8.153476571091089</v>
       </c>
@@ -11053,9 +11014,6 @@
       <c r="O55" t="n">
         <v>751</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>14.4757941013934</v>
       </c>
@@ -11833,9 +11791,6 @@
       <c r="O59" t="n">
         <v>207</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>3.989999173087128</v>
       </c>
@@ -12613,9 +12568,6 @@
       <c r="O63" t="n">
         <v>124</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>2.390144432187458</v>
       </c>
@@ -13393,9 +13345,6 @@
       <c r="O67" t="n">
         <v>29</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.5589853913986798</v>
       </c>
@@ -14173,9 +14122,6 @@
       <c r="O71" t="n">
         <v>3</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -14953,9 +14899,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -15733,9 +15676,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -16513,9 +16453,6 @@
       <c r="O83" t="n">
         <v>2</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -17293,9 +17230,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -18073,9 +18007,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -18853,9 +18784,6 @@
       <c r="O95" t="n">
         <v>9</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.1734782249168317</v>
       </c>
@@ -19633,9 +19561,6 @@
       <c r="O99" t="n">
         <v>43</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.8268362591158698</v>
       </c>
@@ -20413,9 +20338,6 @@
       <c r="O103" t="n">
         <v>434</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>8.345277592006687</v>
       </c>
@@ -21193,9 +21115,6 @@
       <c r="O107" t="n">
         <v>720</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>13.84470015263782</v>
       </c>
@@ -21973,9 +21892,6 @@
       <c r="O111" t="n">
         <v>355</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>6.826206325258925</v>
       </c>
@@ -22753,9 +22669,6 @@
       <c r="O115" t="n">
         <v>58</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>1.115267512295824</v>
       </c>
@@ -23533,9 +23446,6 @@
       <c r="O119" t="n">
         <v>9</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.1730587519079727</v>
       </c>
@@ -24313,9 +24223,6 @@
       <c r="O123" t="n">
         <v>3</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -25093,9 +25000,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -25873,9 +25777,6 @@
       <c r="O131" t="n">
         <v>2</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -26653,9 +26554,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -27433,9 +27331,6 @@
       <c r="O139" t="n">
         <v>5</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -28213,9 +28108,6 @@
       <c r="O143" t="n">
         <v>19</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.3653462540279425</v>
       </c>
@@ -28993,9 +28885,6 @@
       <c r="O147" t="n">
         <v>522</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>10.01351440785505</v>
       </c>
@@ -29773,9 +29662,6 @@
       <c r="O151" t="n">
         <v>397</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>7.615642183751826</v>
       </c>
@@ -30553,9 +30439,6 @@
       <c r="O155" t="n">
         <v>127</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>2.436238179688871</v>
       </c>
@@ -31333,9 +31216,6 @@
       <c r="O159" t="n">
         <v>86</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>1.649736090183015</v>
       </c>
@@ -32113,9 +31993,6 @@
       <c r="O163" t="n">
         <v>52</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.9975148452269395</v>
       </c>
@@ -32893,9 +32770,6 @@
       <c r="O167" t="n">
         <v>14</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.2685616890995606</v>
       </c>
@@ -33673,9 +33547,6 @@
       <c r="O171" t="n">
         <v>4</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -34453,9 +34324,6 @@
       <c r="O175" t="n">
         <v>2</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -35233,9 +35101,6 @@
       <c r="O179" t="n">
         <v>5</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -36013,9 +35878,6 @@
       <c r="O183" t="n">
         <v>5</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -36793,9 +36655,6 @@
       <c r="O187" t="n">
         <v>299</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>5.735710360054902</v>
       </c>
@@ -37573,9 +37432,6 @@
       <c r="O191" t="n">
         <v>2032</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>38.97981087502194</v>
       </c>
@@ -38353,9 +38209,6 @@
       <c r="O195" t="n">
         <v>151</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>2.888212039903997</v>
       </c>
@@ -39133,9 +38986,6 @@
       <c r="O199" t="n">
         <v>23</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.43992633720392</v>
       </c>
@@ -39913,9 +39763,6 @@
       <c r="O203" t="n">
         <v>6</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.1147633923140661</v>
       </c>
@@ -40693,9 +40540,6 @@
       <c r="O207" t="n">
         <v>5</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -41473,9 +41317,6 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -42253,9 +42094,6 @@
       <c r="O215" t="n">
         <v>4</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -43033,9 +42871,6 @@
       <c r="O219" t="n">
         <v>1</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -43813,9 +43648,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -44593,9 +44425,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -45373,9 +45202,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -46153,9 +45979,6 @@
       <c r="O235" t="n">
         <v>2</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -46932,9 +46755,6 @@
       </c>
       <c r="O239" t="n">
         <v>7</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>0</v>
       </c>
       <c r="R239" t="n">
         <v>0.1338906243664104</v>
